--- a/bank customer churn BClassification_project/bank customer churn test data prediction.xlsx
+++ b/bank customer churn BClassification_project/bank customer churn test data prediction.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RPC\Desktop\jupyter files\1-ML &amp; Data Science projects-github\Bank customer churn BClassification_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47EDDB02-EB95-4ED4-A904-827DF6E65423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6D221AD-560C-42E0-942C-A59CAAB90AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,6 +526,8 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.08984375" customWidth="1"/>
+    <col min="12" max="12" width="19.6328125" customWidth="1"/>
+    <col min="18" max="18" width="29.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.35">
@@ -587,7 +589,7 @@
     <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f ca="1">"ID"&amp;RANDBETWEEN(1000,2000)</f>
-        <v>ID1178</v>
+        <v>ID1586</v>
       </c>
       <c r="B2">
         <v>619</v>
@@ -644,7 +646,7 @@
     <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f t="shared" ref="A3:A66" ca="1" si="0">"ID"&amp;RANDBETWEEN(1000,2000)</f>
-        <v>ID1878</v>
+        <v>ID1947</v>
       </c>
       <c r="B3">
         <v>608</v>
@@ -701,7 +703,7 @@
     <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1608</v>
+        <v>ID1650</v>
       </c>
       <c r="B4">
         <v>663</v>
@@ -758,7 +760,7 @@
     <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1188</v>
+        <v>ID1483</v>
       </c>
       <c r="B5">
         <v>742</v>
@@ -815,7 +817,7 @@
     <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1886</v>
+        <v>ID1351</v>
       </c>
       <c r="B6">
         <v>710</v>
@@ -872,7 +874,7 @@
     <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A7" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1131</v>
+        <v>ID1330</v>
       </c>
       <c r="B7">
         <v>710</v>
@@ -929,7 +931,7 @@
     <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A8" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1834</v>
+        <v>ID1148</v>
       </c>
       <c r="B8">
         <v>700</v>
@@ -986,7 +988,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A9" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1861</v>
+        <v>ID1799</v>
       </c>
       <c r="B9">
         <v>720</v>
@@ -1043,7 +1045,7 @@
     <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A10" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1902</v>
+        <v>ID1296</v>
       </c>
       <c r="B10">
         <v>684</v>
@@ -1100,7 +1102,7 @@
     <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A11" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1660</v>
+        <v>ID1139</v>
       </c>
       <c r="B11">
         <v>531</v>
@@ -1157,7 +1159,7 @@
     <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A12" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1101</v>
+        <v>ID1356</v>
       </c>
       <c r="B12">
         <v>742</v>
@@ -1214,7 +1216,7 @@
     <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A13" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1439</v>
+        <v>ID1703</v>
       </c>
       <c r="B13">
         <v>717</v>
@@ -1271,7 +1273,7 @@
     <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A14" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1935</v>
+        <v>ID1883</v>
       </c>
       <c r="B14">
         <v>589</v>
@@ -1328,7 +1330,7 @@
     <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A15" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1603</v>
+        <v>ID1810</v>
       </c>
       <c r="B15">
         <v>767</v>
@@ -1385,7 +1387,7 @@
     <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A16" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1931</v>
+        <v>ID1658</v>
       </c>
       <c r="B16">
         <v>636</v>
@@ -1442,7 +1444,7 @@
     <row r="17" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A17" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1287</v>
+        <v>ID1509</v>
       </c>
       <c r="B17">
         <v>648</v>
@@ -1499,7 +1501,7 @@
     <row r="18" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A18" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1010</v>
+        <v>ID1863</v>
       </c>
       <c r="B18">
         <v>622</v>
@@ -1556,7 +1558,7 @@
     <row r="19" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A19" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1491</v>
+        <v>ID1188</v>
       </c>
       <c r="B19">
         <v>692</v>
@@ -1613,7 +1615,7 @@
     <row r="20" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A20" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1758</v>
+        <v>ID1546</v>
       </c>
       <c r="B20">
         <v>754</v>
@@ -1670,7 +1672,7 @@
     <row r="21" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A21" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1059</v>
+        <v>ID1634</v>
       </c>
       <c r="B21">
         <v>679</v>
@@ -1727,7 +1729,7 @@
     <row r="22" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A22" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1960</v>
+        <v>ID1939</v>
       </c>
       <c r="B22">
         <v>793</v>
@@ -1784,7 +1786,7 @@
     <row r="23" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A23" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1661</v>
+        <v>ID1404</v>
       </c>
       <c r="B23">
         <v>554</v>
@@ -1841,7 +1843,7 @@
     <row r="24" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A24" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1128</v>
+        <v>ID1005</v>
       </c>
       <c r="B24">
         <v>533</v>
@@ -1898,7 +1900,7 @@
     <row r="25" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1878</v>
+        <v>ID1566</v>
       </c>
       <c r="B25">
         <v>658</v>
@@ -1955,7 +1957,7 @@
     <row r="26" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A26" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1065</v>
+        <v>ID1070</v>
       </c>
       <c r="B26">
         <v>713</v>
@@ -2012,7 +2014,7 @@
     <row r="27" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A27" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1527</v>
+        <v>ID1174</v>
       </c>
       <c r="B27">
         <v>711</v>
@@ -2069,7 +2071,7 @@
     <row r="28" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A28" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1932</v>
+        <v>ID1195</v>
       </c>
       <c r="B28">
         <v>669</v>
@@ -2126,7 +2128,7 @@
     <row r="29" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A29" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1291</v>
+        <v>ID1835</v>
       </c>
       <c r="B29">
         <v>439</v>
@@ -2183,7 +2185,7 @@
     <row r="30" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A30" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1710</v>
+        <v>ID1248</v>
       </c>
       <c r="B30">
         <v>763</v>
@@ -2240,7 +2242,7 @@
     <row r="31" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A31" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1691</v>
+        <v>ID1434</v>
       </c>
       <c r="B31">
         <v>697</v>
@@ -2297,7 +2299,7 @@
     <row r="32" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A32" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1244</v>
+        <v>ID1649</v>
       </c>
       <c r="B32">
         <v>702</v>
@@ -2354,7 +2356,7 @@
     <row r="33" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A33" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1017</v>
+        <v>ID1667</v>
       </c>
       <c r="B33">
         <v>686</v>
@@ -2411,7 +2413,7 @@
     <row r="34" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A34" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1144</v>
+        <v>ID1513</v>
       </c>
       <c r="B34">
         <v>629</v>
@@ -2468,7 +2470,7 @@
     <row r="35" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A35" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1011</v>
+        <v>ID1782</v>
       </c>
       <c r="B35">
         <v>823</v>
@@ -2525,7 +2527,7 @@
     <row r="36" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A36" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1191</v>
+        <v>ID1993</v>
       </c>
       <c r="B36">
         <v>683</v>
@@ -2582,7 +2584,7 @@
     <row r="37" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A37" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1424</v>
+        <v>ID1241</v>
       </c>
       <c r="B37">
         <v>555</v>
@@ -2639,7 +2641,7 @@
     <row r="38" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A38" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1993</v>
+        <v>ID1126</v>
       </c>
       <c r="B38">
         <v>647</v>
@@ -2696,7 +2698,7 @@
     <row r="39" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A39" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1285</v>
+        <v>ID1006</v>
       </c>
       <c r="B39">
         <v>714</v>
@@ -2753,7 +2755,7 @@
     <row r="40" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A40" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1412</v>
+        <v>ID1083</v>
       </c>
       <c r="B40">
         <v>850</v>
@@ -2810,7 +2812,7 @@
     <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A41" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1671</v>
+        <v>ID1828</v>
       </c>
       <c r="B41">
         <v>788</v>
@@ -2867,7 +2869,7 @@
     <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A42" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1832</v>
+        <v>ID1906</v>
       </c>
       <c r="B42">
         <v>798</v>
@@ -2924,7 +2926,7 @@
     <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A43" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1996</v>
+        <v>ID1830</v>
       </c>
       <c r="B43">
         <v>770</v>
@@ -2981,7 +2983,7 @@
     <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1053</v>
+        <v>ID1563</v>
       </c>
       <c r="B44">
         <v>569</v>
@@ -3038,7 +3040,7 @@
     <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A45" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1082</v>
+        <v>ID1694</v>
       </c>
       <c r="B45">
         <v>425</v>
@@ -3095,7 +3097,7 @@
     <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A46" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1196</v>
+        <v>ID1735</v>
       </c>
       <c r="B46">
         <v>547</v>
@@ -3152,7 +3154,7 @@
     <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A47" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1867</v>
+        <v>ID1975</v>
       </c>
       <c r="B47">
         <v>725</v>
@@ -3209,7 +3211,7 @@
     <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A48" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1292</v>
+        <v>ID1708</v>
       </c>
       <c r="B48">
         <v>506</v>
@@ -3266,7 +3268,7 @@
     <row r="49" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A49" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1628</v>
+        <v>ID1641</v>
       </c>
       <c r="B49">
         <v>632</v>
@@ -3323,7 +3325,7 @@
     <row r="50" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A50" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1886</v>
+        <v>ID1576</v>
       </c>
       <c r="B50">
         <v>620</v>
@@ -3380,7 +3382,7 @@
     <row r="51" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A51" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1015</v>
+        <v>ID1720</v>
       </c>
       <c r="B51">
         <v>663</v>
@@ -3437,7 +3439,7 @@
     <row r="52" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A52" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1077</v>
+        <v>ID1408</v>
       </c>
       <c r="B52">
         <v>700</v>
@@ -3494,7 +3496,7 @@
     <row r="53" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A53" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1349</v>
+        <v>ID1983</v>
       </c>
       <c r="B53">
         <v>696</v>
@@ -3551,7 +3553,7 @@
     <row r="54" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A54" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1982</v>
+        <v>ID1848</v>
       </c>
       <c r="B54">
         <v>767</v>
@@ -3608,7 +3610,7 @@
     <row r="55" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A55" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1481</v>
+        <v>ID1622</v>
       </c>
       <c r="B55">
         <v>561</v>
@@ -3665,7 +3667,7 @@
     <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1706</v>
+        <v>ID1063</v>
       </c>
       <c r="B56">
         <v>350</v>
@@ -3722,7 +3724,7 @@
     <row r="57" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A57" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1665</v>
+        <v>ID1544</v>
       </c>
       <c r="B57">
         <v>706</v>
@@ -3779,7 +3781,7 @@
     <row r="58" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A58" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1869</v>
+        <v>ID1926</v>
       </c>
       <c r="B58">
         <v>464</v>
@@ -3836,7 +3838,7 @@
     <row r="59" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A59" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1577</v>
+        <v>ID1955</v>
       </c>
       <c r="B59">
         <v>501</v>
@@ -3893,7 +3895,7 @@
     <row r="60" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A60" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1220</v>
+        <v>ID1703</v>
       </c>
       <c r="B60">
         <v>625</v>
@@ -3950,7 +3952,7 @@
     <row r="61" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A61" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1512</v>
+        <v>ID1740</v>
       </c>
       <c r="B61">
         <v>535</v>
@@ -4007,7 +4009,7 @@
     <row r="62" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A62" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1099</v>
+        <v>ID1441</v>
       </c>
       <c r="B62">
         <v>786</v>
@@ -4064,7 +4066,7 @@
     <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A63" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1010</v>
+        <v>ID1077</v>
       </c>
       <c r="B63">
         <v>620</v>
@@ -4121,7 +4123,7 @@
     <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1433</v>
+        <v>ID1736</v>
       </c>
       <c r="B64">
         <v>605</v>
@@ -4178,7 +4180,7 @@
     <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A65" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1055</v>
+        <v>ID1652</v>
       </c>
       <c r="B65">
         <v>670</v>
@@ -4235,7 +4237,7 @@
     <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>ID1941</v>
+        <v>ID1962</v>
       </c>
       <c r="B66">
         <v>617</v>
@@ -4292,7 +4294,7 @@
     <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" t="str">
         <f t="shared" ref="A67:A100" ca="1" si="1">"ID"&amp;RANDBETWEEN(1000,2000)</f>
-        <v>ID1942</v>
+        <v>ID1816</v>
       </c>
       <c r="B67">
         <v>595</v>
@@ -4349,7 +4351,7 @@
     <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1756</v>
+        <v>ID1568</v>
       </c>
       <c r="B68">
         <v>687</v>
@@ -4406,7 +4408,7 @@
     <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1216</v>
+        <v>ID1825</v>
       </c>
       <c r="B69">
         <v>757</v>
@@ -4463,7 +4465,7 @@
     <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1026</v>
+        <v>ID1270</v>
       </c>
       <c r="B70">
         <v>746</v>
@@ -4520,7 +4522,7 @@
     <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1199</v>
+        <v>ID1920</v>
       </c>
       <c r="B71">
         <v>503</v>
@@ -4577,7 +4579,7 @@
     <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1221</v>
+        <v>ID1305</v>
       </c>
       <c r="B72">
         <v>543</v>
@@ -4634,7 +4636,7 @@
     <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A73" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1995</v>
+        <v>ID1565</v>
       </c>
       <c r="B73">
         <v>428</v>
@@ -4691,7 +4693,7 @@
     <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1450</v>
+        <v>ID1798</v>
       </c>
       <c r="B74">
         <v>768</v>
@@ -4748,7 +4750,7 @@
     <row r="75" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A75" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1373</v>
+        <v>ID1365</v>
       </c>
       <c r="B75">
         <v>618</v>
@@ -4805,7 +4807,7 @@
     <row r="76" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A76" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1991</v>
+        <v>ID1899</v>
       </c>
       <c r="B76">
         <v>591</v>
@@ -4862,7 +4864,7 @@
     <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1210</v>
+        <v>ID1145</v>
       </c>
       <c r="B77">
         <v>658</v>
@@ -4919,7 +4921,7 @@
     <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1900</v>
+        <v>ID1014</v>
       </c>
       <c r="B78">
         <v>625</v>
@@ -4976,7 +4978,7 @@
     <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1852</v>
+        <v>ID1253</v>
       </c>
       <c r="B79">
         <v>717</v>
@@ -5033,7 +5035,7 @@
     <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1925</v>
+        <v>ID1281</v>
       </c>
       <c r="B80">
         <v>667</v>
@@ -5090,7 +5092,7 @@
     <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A81" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1871</v>
+        <v>ID1819</v>
       </c>
       <c r="B81">
         <v>804</v>
@@ -5147,7 +5149,7 @@
     <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A82" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1309</v>
+        <v>ID1996</v>
       </c>
       <c r="B82">
         <v>693</v>
@@ -5204,7 +5206,7 @@
     <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A83" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1225</v>
+        <v>ID1666</v>
       </c>
       <c r="B83">
         <v>729</v>
@@ -5261,7 +5263,7 @@
     <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A84" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1692</v>
+        <v>ID1151</v>
       </c>
       <c r="B84">
         <v>484</v>
@@ -5318,7 +5320,7 @@
     <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A85" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1195</v>
+        <v>ID1425</v>
       </c>
       <c r="B85">
         <v>632</v>
@@ -5375,7 +5377,7 @@
     <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A86" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1576</v>
+        <v>ID1282</v>
       </c>
       <c r="B86">
         <v>536</v>
@@ -5432,7 +5434,7 @@
     <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A87" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1058</v>
+        <v>ID1104</v>
       </c>
       <c r="B87">
         <v>573</v>
@@ -5489,7 +5491,7 @@
     <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A88" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1375</v>
+        <v>ID1846</v>
       </c>
       <c r="B88">
         <v>655</v>
@@ -5546,7 +5548,7 @@
     <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A89" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1653</v>
+        <v>ID1181</v>
       </c>
       <c r="B89">
         <v>666</v>
@@ -5603,7 +5605,7 @@
     <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1009</v>
+        <v>ID1168</v>
       </c>
       <c r="B90">
         <v>726</v>
@@ -5660,7 +5662,7 @@
     <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1611</v>
+        <v>ID1413</v>
       </c>
       <c r="B91">
         <v>523</v>
@@ -5717,7 +5719,7 @@
     <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1358</v>
+        <v>ID1471</v>
       </c>
       <c r="B92">
         <v>728</v>
@@ -5774,7 +5776,7 @@
     <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1919</v>
+        <v>ID1933</v>
       </c>
       <c r="B93">
         <v>701</v>
@@ -5831,7 +5833,7 @@
     <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1211</v>
+        <v>ID1756</v>
       </c>
       <c r="B94">
         <v>518</v>
@@ -5888,7 +5890,7 @@
     <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1380</v>
+        <v>ID1705</v>
       </c>
       <c r="B95">
         <v>808</v>
@@ -5945,7 +5947,7 @@
     <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1633</v>
+        <v>ID1018</v>
       </c>
       <c r="B96">
         <v>641</v>
@@ -6002,7 +6004,7 @@
     <row r="97" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A97" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1305</v>
+        <v>ID1001</v>
       </c>
       <c r="B97">
         <v>700</v>
@@ -6059,7 +6061,7 @@
     <row r="98" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A98" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1367</v>
+        <v>ID1597</v>
       </c>
       <c r="B98">
         <v>660</v>
@@ -6116,7 +6118,7 @@
     <row r="99" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A99" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1786</v>
+        <v>ID1819</v>
       </c>
       <c r="B99">
         <v>615</v>
@@ -6173,7 +6175,7 @@
     <row r="100" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A100" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>ID1313</v>
+        <v>ID1952</v>
       </c>
       <c r="B100">
         <v>705</v>
